--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2426-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2426-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{998F3131-E194-43D2-B7D3-B3C8A52C4D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20188C95-70B2-49D1-9D7B-179269F3A5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{964E6490-70A9-4387-863B-197DB753C614}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{04ED2CFF-5404-40B2-8E52-23F4507F30D0}"/>
   </bookViews>
   <sheets>
     <sheet name="2426-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1460,21 +1460,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DBA1983-71E8-4B6E-9DD9-5D1F58D478F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917CF7F7-E5D3-4D54-A949-524AE1AA9743}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1502,7 +1502,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1628,7 +1628,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
         <v>2024</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="38">
         <v>2023</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2022</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>25</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2021</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2020</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>25</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>25</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2019</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2018</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2017</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2016</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2015</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2014</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2013</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2012</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2011</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2010</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2009</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2008</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2007</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2006</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2005</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2004</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2003</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2002</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2001</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2000</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>1999</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>1998</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>1997</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>1996</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>1995</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>1994</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>1993</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40" t="s">
         <v>38</v>
       </c>
